--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2307,57 +2307,61 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103703852</v>
+        <v>137177094</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>43500</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>101242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Blajkvät, SO om Hejde, Gtl</t>
+          <t>9. N Gajstmyrvägen, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700895</v>
+        <v>700816</v>
       </c>
       <c r="R16" t="n">
-        <v>6366844</v>
+        <v>6366287</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2381,17 +2385,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gamla gnagspår på tallåga, omkr ca. 100 cm.</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,91 +2403,85 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Äldre, senvuxen kalktallskog.</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+          <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103703852</t>
+          <t>https://artportalen.se/Sighting/137177094</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103703846</v>
+        <v>137177099</v>
       </c>
       <c r="B17" t="n">
-        <v>99096</v>
+        <v>43500</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Blajkvät, SO om Hejde, Gtl</t>
+          <t>9. N Gajstmyrvägen, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700996</v>
+        <v>700811</v>
       </c>
       <c r="R17" t="n">
-        <v>6366972</v>
+        <v>6366320</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2512,12 +2505,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2530,77 +2523,85 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Äldre, senvuxen kalktallskog.</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+          <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103703846</t>
+          <t>https://artportalen.se/Sighting/137177099</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120492759</v>
+        <v>137177108</v>
       </c>
       <c r="B18" t="n">
-        <v>99096</v>
+        <v>43500</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Utskogen, Utskogen, Gtl</t>
+          <t>9. N Gajstmyrvägen, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700973</v>
+        <v>700807</v>
       </c>
       <c r="R18" t="n">
-        <v>6366729</v>
+        <v>6366410</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2624,12 +2625,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2638,33 +2639,38 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120492759</t>
+          <t>https://artportalen.se/Sighting/137177108</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120492809</v>
+        <v>103703852</v>
       </c>
       <c r="B19" t="n">
-        <v>99096</v>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,34 +2678,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Utskogen, Utskogen, Gtl</t>
+          <t>Blajkvät, SO om Hejde, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>701013</v>
+        <v>700895</v>
       </c>
       <c r="R19" t="n">
-        <v>6366707</v>
+        <v>6366844</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2726,12 +2741,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gamla gnagspår på tallåga, omkr ca. 100 cm.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2740,30 +2760,50 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Äldre, senvuxen kalktallskog.</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120492809</t>
+          <t>https://artportalen.se/Sighting/103703852</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120493244</v>
+        <v>103703846</v>
       </c>
       <c r="B20" t="n">
         <v>99096</v>
@@ -2792,16 +2832,20 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bruten, Bruten, Gtl</t>
+          <t>Blajkvät, SO om Hejde, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700590</v>
+        <v>700996</v>
       </c>
       <c r="R20" t="n">
-        <v>6366381</v>
+        <v>6366972</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2828,12 +2872,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2842,30 +2886,40 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre, senvuxen kalktallskog.</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120493244</t>
+          <t>https://artportalen.se/Sighting/103703846</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120493304</v>
+        <v>120492759</v>
       </c>
       <c r="B21" t="n">
         <v>99096</v>
@@ -2896,14 +2950,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bruten, Bruten, Gtl</t>
+          <t>Utskogen, Utskogen, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700590</v>
+        <v>700973</v>
       </c>
       <c r="R21" t="n">
-        <v>6366339</v>
+        <v>6366729</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2961,13 +3015,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120493304</t>
+          <t>https://artportalen.se/Sighting/120492759</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120493452</v>
+        <v>120492809</v>
       </c>
       <c r="B22" t="n">
         <v>99096</v>
@@ -2998,14 +3052,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bruten, Bruten, Gtl</t>
+          <t>Utskogen, Utskogen, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700548</v>
+        <v>701013</v>
       </c>
       <c r="R22" t="n">
-        <v>6366234</v>
+        <v>6366707</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3063,16 +3117,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120493452</t>
+          <t>https://artportalen.se/Sighting/120492809</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103703850</v>
+        <v>120493244</v>
       </c>
       <c r="B23" t="n">
-        <v>99141</v>
+        <v>99096</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3080,50 +3134,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Blajkvät, SO om Hejde, Gtl</t>
+          <t>Bruten, Bruten, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>701005</v>
+        <v>700590</v>
       </c>
       <c r="R23" t="n">
-        <v>6366913</v>
+        <v>6366381</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,17 +3188,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>1 vinterståndare.</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3169,43 +3202,33 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Äldre, senvuxen kalktallskog.</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103703850</t>
+          <t>https://artportalen.se/Sighting/120493244</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125769803</v>
+        <v>120493304</v>
       </c>
       <c r="B24" t="n">
-        <v>99147</v>
+        <v>99096</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3213,41 +3236,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219864</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Utskogen, Gtl</t>
+          <t>Bruten, Bruten, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>701037</v>
+        <v>700590</v>
       </c>
       <c r="R24" t="n">
-        <v>6366934</v>
+        <v>6366339</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3271,22 +3290,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3301,62 +3310,62 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Karin Berg Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125769803</t>
+          <t>https://artportalen.se/Sighting/120493304</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103733446</v>
+        <v>120493452</v>
       </c>
       <c r="B25" t="n">
-        <v>108116</v>
+        <v>99096</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Väntinge, Gtl</t>
+          <t>Bruten, Bruten, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700544</v>
+        <v>700548</v>
       </c>
       <c r="R25" t="n">
-        <v>6366239</v>
+        <v>6366234</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3383,12 +3392,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3403,66 +3412,78 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103733446</t>
+          <t>https://artportalen.se/Sighting/120493452</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103733447</v>
+        <v>103703850</v>
       </c>
       <c r="B26" t="n">
-        <v>108116</v>
+        <v>99141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220079</v>
+        <v>219862</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Väntinge, Gtl</t>
+          <t>Blajkvät, SO om Hejde, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700494</v>
+        <v>701005</v>
       </c>
       <c r="R26" t="n">
-        <v>6366137</v>
+        <v>6366913</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3489,12 +3510,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1 vinterståndare.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3503,18 +3529,24 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Äldre, senvuxen kalktallskog.</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3524,54 +3556,58 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103733447</t>
+          <t>https://artportalen.se/Sighting/103703850</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120493232</v>
+        <v>125769803</v>
       </c>
       <c r="B27" t="n">
-        <v>104640</v>
+        <v>99147</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220164</v>
+        <v>219864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bruten, Bruten, Gtl</t>
+          <t>Utskogen, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700582</v>
+        <v>701037</v>
       </c>
       <c r="R27" t="n">
-        <v>6366394</v>
+        <v>6366934</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3595,12 +3631,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3615,27 +3661,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Karin Berg Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120493232</t>
+          <t>https://artportalen.se/Sighting/125769803</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120493229</v>
+        <v>103733446</v>
       </c>
       <c r="B28" t="n">
-        <v>107517</v>
+        <v>108116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3643,34 +3689,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bruten, Bruten, Gtl</t>
+          <t>Väntinge, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700582</v>
+        <v>700544</v>
       </c>
       <c r="R28" t="n">
-        <v>6366393</v>
+        <v>6366239</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3697,12 +3743,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3717,27 +3763,31 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120493229</t>
+          <t>https://artportalen.se/Sighting/103733446</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120493421</v>
+        <v>103733447</v>
       </c>
       <c r="B29" t="n">
-        <v>107517</v>
+        <v>108116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3745,34 +3795,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bruten, Bruten, Gtl</t>
+          <t>Väntinge, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700541</v>
+        <v>700494</v>
       </c>
       <c r="R29" t="n">
-        <v>6366241</v>
+        <v>6366137</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3799,12 +3849,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3819,62 +3869,66 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120493421</t>
+          <t>https://artportalen.se/Sighting/103733447</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120506912</v>
+        <v>120493232</v>
       </c>
       <c r="B30" t="n">
-        <v>87262</v>
+        <v>104640</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>248956</v>
+        <v>220164</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Klinte, Gtl</t>
+          <t>Bruten, Bruten, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700628</v>
+        <v>700582</v>
       </c>
       <c r="R30" t="n">
-        <v>6366355</v>
+        <v>6366394</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3909,11 +3963,6 @@
           <t>2024-10-19</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Flera små fruktkroppar inne i en liten grandunge</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3926,66 +3975,62 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna Träff</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Träff</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120506912</t>
+          <t>https://artportalen.se/Sighting/120493232</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120507147</v>
+        <v>120493229</v>
       </c>
       <c r="B31" t="n">
-        <v>87262</v>
+        <v>107517</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>248956</v>
+        <v>221849</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Bruten, Bruten, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700694</v>
+        <v>700582</v>
       </c>
       <c r="R31" t="n">
-        <v>6366357</v>
+        <v>6366393</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4032,66 +4077,62 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120507147</t>
+          <t>https://artportalen.se/Sighting/120493229</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120507148</v>
+        <v>120493421</v>
       </c>
       <c r="B32" t="n">
-        <v>87262</v>
+        <v>107517</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>248956</v>
+        <v>221849</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Bruten, Bruten, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700662</v>
+        <v>700541</v>
       </c>
       <c r="R32" t="n">
-        <v>6366303</v>
+        <v>6366241</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4138,66 +4179,62 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Annica Beil</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120507148</t>
+          <t>https://artportalen.se/Sighting/120493421</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120507146</v>
+        <v>120506912</v>
       </c>
       <c r="B33" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Klinte, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700621</v>
+        <v>700628</v>
       </c>
       <c r="R33" t="n">
-        <v>6366367</v>
+        <v>6366355</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4232,6 +4269,11 @@
           <t>2024-10-19</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Flera små fruktkroppar inne i en liten grandunge</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4244,20 +4286,338 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
+          <t>Anna Träff</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anna Träff</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120506912</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120507147</v>
+      </c>
+      <c r="B34" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>700694</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6366357</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
           <t>Annica Beil</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
+      <c r="AX34" t="inlineStr">
         <is>
           <t>Annica Beil</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr">
+      <c r="AY34" t="inlineStr">
         <is>
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507147</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120507148</v>
+      </c>
+      <c r="B35" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>700662</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6366303</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120507148</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120507146</v>
+      </c>
+      <c r="B36" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>700621</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6366367</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Annica Beil</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120507146</t>
         </is>
@@ -4297,6 +4657,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -2310,7 +2310,7 @@
         <v>137177094</v>
       </c>
       <c r="B16" t="n">
-        <v>43500</v>
+        <v>43513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>137177099</v>
       </c>
       <c r="B17" t="n">
-        <v>43500</v>
+        <v>43513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>137177108</v>
       </c>
       <c r="B18" t="n">
-        <v>43500</v>
+        <v>43513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -2310,7 +2310,7 @@
         <v>137177094</v>
       </c>
       <c r="B16" t="n">
-        <v>43513</v>
+        <v>43515</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>137177099</v>
       </c>
       <c r="B17" t="n">
-        <v>43513</v>
+        <v>43515</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>137177108</v>
       </c>
       <c r="B18" t="n">
-        <v>43513</v>
+        <v>43515</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -2341,11 +2341,7 @@
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2461,11 +2457,7 @@
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2581,11 +2573,7 @@
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -2310,7 +2310,7 @@
         <v>137177094</v>
       </c>
       <c r="B16" t="n">
-        <v>43515</v>
+        <v>43525</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137177099</v>
       </c>
       <c r="B17" t="n">
-        <v>43515</v>
+        <v>43525</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>137177108</v>
       </c>
       <c r="B18" t="n">
-        <v>43515</v>
+        <v>43525</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 62132-2023 artfynd.xlsx
+++ b/artfynd/A 62132-2023 artfynd.xlsx
@@ -2310,7 +2310,7 @@
         <v>137177094</v>
       </c>
       <c r="B16" t="n">
-        <v>43525</v>
+        <v>43526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137177099</v>
       </c>
       <c r="B17" t="n">
-        <v>43525</v>
+        <v>43526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>137177108</v>
       </c>
       <c r="B18" t="n">
-        <v>43525</v>
+        <v>43526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
